--- a/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{A2D51B21-B9A4-4E12-9722-14A2852C5BB5}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{E0D9E4F7-8B4B-45A4-8AA3-D32EBB97DEC1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="BFLU" r:id="rId1" sheetId="1"/>
-    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
+    <sheet name="BFLU_1Result" r:id="rId2" sheetId="3"/>
+    <sheet name="BFLUError" r:id="rId3" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="137">
   <si>
     <t>Result</t>
   </si>
@@ -283,73 +284,175 @@
     <t>Tue Mar 24 19:00:20 IST 2026</t>
   </si>
   <si>
+    <t>Tue Mar 24 19:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:12:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:13:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:13:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:14:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:15:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:16:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:18:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:19:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:20:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:21:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:21:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:22:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:23:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:23:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:24:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 19:24:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Payment app+ 1st + 2nd +3rd lookup</t>
+  </si>
+  <si>
+    <t>Payment app+ Company Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment app+ CAN </t>
+  </si>
+  <si>
+    <t>Bijita Companys</t>
+  </si>
+  <si>
+    <t>45332116803cA</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:37:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:39:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:40:40 IST 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Tue Mar 24 19:11:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:12:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:13:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:13:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:14:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:14:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:15:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:16:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:16:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:17:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:18:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:18:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:19:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:20:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:20:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:21:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:21:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:22:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:23:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:23:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:24:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 24 19:24:58 IST 2026</t>
+    <t>Thu Apr 23 16:44:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:45:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:47:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:48:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:48:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:49:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:50:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:50:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:51:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:52:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:52:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:53:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:53:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:55:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:55:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:56:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:56:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:57:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:58:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:58:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:59:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 16:59:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 17:00:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 17:01:08 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -417,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -439,6 +542,9 @@
     </xf>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,10 +937,13 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>71</v>
@@ -848,10 +957,13 @@
         <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>71</v>
@@ -865,10 +977,13 @@
         <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>71</v>
@@ -882,7 +997,7 @@
         <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -898,8 +1013,12 @@
       </c>
     </row>
     <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6"/>
-      <c r="B6"/>
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
       <c r="C6" s="6" t="s">
         <v>55</v>
       </c>
@@ -914,8 +1033,12 @@
       </c>
     </row>
     <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7"/>
-      <c r="B7"/>
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
@@ -930,8 +1053,12 @@
       </c>
     </row>
     <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8"/>
-      <c r="B8"/>
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
@@ -946,8 +1073,12 @@
       </c>
     </row>
     <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9"/>
-      <c r="B9"/>
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
@@ -977,8 +1108,12 @@
       </c>
     </row>
     <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10"/>
-      <c r="B10"/>
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
@@ -996,8 +1131,12 @@
       </c>
     </row>
     <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11"/>
-      <c r="B11"/>
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
       </c>
@@ -1015,8 +1154,12 @@
       </c>
     </row>
     <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12"/>
-      <c r="B12"/>
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
       <c r="C12" s="6" t="s">
         <v>38</v>
       </c>
@@ -1034,8 +1177,12 @@
       </c>
     </row>
     <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13"/>
-      <c r="B13"/>
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
       </c>
@@ -1053,8 +1200,12 @@
       </c>
     </row>
     <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14"/>
-      <c r="B14"/>
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>123</v>
+      </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
       </c>
@@ -1072,8 +1223,12 @@
       </c>
     </row>
     <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15"/>
-      <c r="B15"/>
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
@@ -1091,8 +1246,12 @@
       </c>
     </row>
     <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16"/>
-      <c r="B16"/>
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>125</v>
+      </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
       </c>
@@ -1110,8 +1269,12 @@
       </c>
     </row>
     <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17"/>
-      <c r="B17"/>
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>126</v>
+      </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
       </c>
@@ -1129,8 +1292,12 @@
       </c>
     </row>
     <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18"/>
-      <c r="B18"/>
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>127</v>
+      </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
       </c>
@@ -1148,8 +1315,12 @@
       </c>
     </row>
     <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19"/>
-      <c r="B19"/>
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
       </c>
@@ -1167,8 +1338,12 @@
       </c>
     </row>
     <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20"/>
-      <c r="B20"/>
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>129</v>
+      </c>
       <c r="C20" s="6" t="s">
         <v>57</v>
       </c>
@@ -1186,8 +1361,12 @@
       </c>
     </row>
     <row ht="25" r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21"/>
-      <c r="B21"/>
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>130</v>
+      </c>
       <c r="C21" s="6" t="s">
         <v>54</v>
       </c>
@@ -1208,8 +1387,12 @@
       </c>
     </row>
     <row customHeight="1" ht="18" r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22"/>
-      <c r="B22"/>
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>131</v>
+      </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
       </c>
@@ -1227,8 +1410,12 @@
       </c>
     </row>
     <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23"/>
-      <c r="B23"/>
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>132</v>
+      </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
       </c>
@@ -1246,8 +1433,12 @@
       </c>
     </row>
     <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24"/>
-      <c r="B24"/>
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>133</v>
+      </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
       </c>
@@ -1265,8 +1456,12 @@
       </c>
     </row>
     <row customHeight="1" ht="17.5" r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25"/>
-      <c r="B25"/>
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
       </c>
@@ -1284,8 +1479,12 @@
       </c>
     </row>
     <row ht="13" r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26"/>
-      <c r="B26"/>
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
@@ -1303,8 +1502,12 @@
       </c>
     </row>
     <row ht="13" r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27"/>
-      <c r="B27"/>
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
       <c r="C27" s="6" t="s">
         <v>59</v>
       </c>
@@ -1329,6 +1532,132 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A22EE10-F9D4-4571-858C-1BE3B4ED1851}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
+    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="3" width="24.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
+    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="3">
+        <v>12162016297</v>
+      </c>
+      <c r="J2" s="3">
+        <v>12162016298</v>
+      </c>
+      <c r="K2" s="7">
+        <v>12162016299</v>
+      </c>
+    </row>
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -1391,7 +1720,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1414,7 +1743,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1437,7 +1766,7 @@
         <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1460,7 +1789,7 @@
         <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1483,7 +1812,7 @@
         <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>39</v>
@@ -1506,7 +1835,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>40</v>
@@ -1529,7 +1858,7 @@
         <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>41</v>
@@ -1555,7 +1884,7 @@
         <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>42</v>
@@ -1581,7 +1910,7 @@
         <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -1607,7 +1936,7 @@
         <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>43</v>
@@ -1633,7 +1962,7 @@
         <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>49</v>
@@ -1659,7 +1988,7 @@
         <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>50</v>
@@ -1685,7 +2014,7 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>51</v>
@@ -1711,7 +2040,7 @@
         <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>45</v>
@@ -1737,7 +2066,7 @@
         <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>46</v>
@@ -1763,7 +2092,7 @@
         <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>47</v>
@@ -1789,7 +2118,7 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>48</v>
@@ -1815,7 +2144,7 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>64</v>
@@ -1838,7 +2167,7 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>66</v>
@@ -1864,7 +2193,7 @@
         <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>67</v>
@@ -1890,7 +2219,7 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>68</v>
@@ -1916,7 +2245,7 @@
         <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>69</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="266">
   <si>
     <t>Result</t>
   </si>
@@ -453,6 +453,393 @@
   </si>
   <si>
     <t>Thu Apr 23 17:01:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:36:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:37:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:38:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:39:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:41:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:41:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:42:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:43:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:44:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:45:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:46:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:48:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:49:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:49:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:50:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:51:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:52:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:53:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:53:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:54:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:55:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:55:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:57:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:58:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 09:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:00:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:01:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:02:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:03:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:03:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:04:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:05:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:05:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:06:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:07:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:07:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:08:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:09:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:09:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:12:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:12:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:14:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:14:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:15:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:16:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:16:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:18:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:18:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:20:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:20:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:21:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:21:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:22:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:23:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:24:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:25:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:25:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:26:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:27:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:28:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:28:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:30:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:31:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:31:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:32:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:33:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:34:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:35:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:35:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:36:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:37:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:38:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:39:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:40:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:41:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:41:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:43:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:44:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:45:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:46:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:47:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:48:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:48:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:50:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:52:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:52:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:53:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:54:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:55:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:55:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:56:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:57:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:57:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:58:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:59:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 10:59:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:00:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:00:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:01:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:02:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:03:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:04:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:05:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:05:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:06:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:07:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:07:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:08:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -880,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
@@ -933,11 +1320,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
+      <c r="A2" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>215</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -953,11 +1340,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="3">
         <v>76</v>
       </c>
-      <c r="B3" t="s">
-        <v>112</v>
+      <c r="B3" t="s" s="3">
+        <v>216</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -973,11 +1360,11 @@
       </c>
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="3">
         <v>76</v>
       </c>
-      <c r="B4" t="s">
-        <v>113</v>
+      <c r="B4" t="s" s="3">
+        <v>217</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -993,11 +1380,11 @@
       </c>
     </row>
     <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="3">
         <v>76</v>
       </c>
-      <c r="B5" t="s">
-        <v>114</v>
+      <c r="B5" t="s" s="3">
+        <v>218</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1013,11 +1400,11 @@
       </c>
     </row>
     <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s">
-        <v>115</v>
+      <c r="A6" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>219</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>55</v>
@@ -1033,11 +1420,11 @@
       </c>
     </row>
     <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>116</v>
+      <c r="A7" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s" s="3">
+        <v>220</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1053,11 +1440,11 @@
       </c>
     </row>
     <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" t="s">
-        <v>117</v>
+      <c r="A8" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s" s="3">
+        <v>221</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1073,11 +1460,11 @@
       </c>
     </row>
     <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>118</v>
+      <c r="A9" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s" s="3">
+        <v>222</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1108,11 +1495,11 @@
       </c>
     </row>
     <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" t="s">
-        <v>119</v>
+      <c r="A10" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>223</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1131,11 +1518,11 @@
       </c>
     </row>
     <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="3">
         <v>76</v>
       </c>
-      <c r="B11" t="s">
-        <v>120</v>
+      <c r="B11" t="s" s="3">
+        <v>224</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1154,11 +1541,11 @@
       </c>
     </row>
     <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="3">
         <v>76</v>
       </c>
-      <c r="B12" t="s">
-        <v>121</v>
+      <c r="B12" t="s" s="3">
+        <v>225</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>38</v>
@@ -1177,11 +1564,11 @@
       </c>
     </row>
     <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" t="s">
-        <v>122</v>
+      <c r="A13" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s" s="3">
+        <v>226</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1200,11 +1587,11 @@
       </c>
     </row>
     <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>123</v>
+      <c r="A14" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s" s="3">
+        <v>227</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1223,11 +1610,11 @@
       </c>
     </row>
     <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>124</v>
+      <c r="A15" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s" s="3">
+        <v>228</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1246,11 +1633,11 @@
       </c>
     </row>
     <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" t="s">
-        <v>125</v>
+      <c r="A16" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s" s="3">
+        <v>229</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1269,11 +1656,11 @@
       </c>
     </row>
     <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" t="s">
-        <v>126</v>
+      <c r="A17" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s" s="3">
+        <v>230</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
@@ -1292,11 +1679,11 @@
       </c>
     </row>
     <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>127</v>
+      <c r="A18" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s" s="3">
+        <v>231</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1315,11 +1702,11 @@
       </c>
     </row>
     <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>128</v>
+      <c r="A19" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s" s="3">
+        <v>232</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1338,11 +1725,11 @@
       </c>
     </row>
     <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s">
-        <v>129</v>
+      <c r="A20" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s" s="3">
+        <v>233</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>57</v>
@@ -1361,11 +1748,11 @@
       </c>
     </row>
     <row ht="25" r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" t="s">
-        <v>130</v>
+      <c r="A21" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s" s="3">
+        <v>234</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>54</v>
@@ -1387,11 +1774,11 @@
       </c>
     </row>
     <row customHeight="1" ht="18" r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s">
-        <v>131</v>
+      <c r="A22" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="3">
+        <v>235</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1410,11 +1797,11 @@
       </c>
     </row>
     <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s">
-        <v>132</v>
+      <c r="A23" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="3">
+        <v>236</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1433,11 +1820,11 @@
       </c>
     </row>
     <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s">
-        <v>133</v>
+      <c r="A24" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s" s="3">
+        <v>237</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
@@ -1456,11 +1843,11 @@
       </c>
     </row>
     <row customHeight="1" ht="17.5" r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" t="s">
-        <v>134</v>
+      <c r="A25" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s" s="3">
+        <v>238</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1479,11 +1866,11 @@
       </c>
     </row>
     <row ht="13" r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" t="s">
-        <v>135</v>
+      <c r="A26" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s" s="3">
+        <v>239</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1502,11 +1889,11 @@
       </c>
     </row>
     <row ht="13" r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" t="s">
-        <v>136</v>
+      <c r="A27" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s" s="3">
+        <v>240</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>59</v>
@@ -1533,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A22EE10-F9D4-4571-858C-1BE3B4ED1851}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
@@ -1586,11 +1973,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>107</v>
+      <c r="A2" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>241</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>102</v>
@@ -1612,13 +1999,13 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>242</v>
+      </c>
+      <c r="C3" t="s" s="6">
         <v>103</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1632,13 +2019,13 @@
       </c>
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>243</v>
+      </c>
+      <c r="C4" t="s" s="6">
         <v>104</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1659,7 +2046,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
@@ -1716,11 +2103,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
+      <c r="A2" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s" s="5">
+        <v>244</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1739,11 +2126,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>81</v>
+      <c r="A3" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s" s="5">
+        <v>245</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1762,11 +2149,11 @@
       </c>
     </row>
     <row customHeight="1" ht="14.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>82</v>
+      <c r="A4" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s" s="5">
+        <v>246</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1785,11 +2172,11 @@
       </c>
     </row>
     <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s">
-        <v>83</v>
+      <c r="A5" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s" s="5">
+        <v>247</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1808,11 +2195,11 @@
       </c>
     </row>
     <row ht="13" r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" t="s">
-        <v>84</v>
+      <c r="A6" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s" s="5">
+        <v>248</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>39</v>
@@ -1831,11 +2218,11 @@
       </c>
     </row>
     <row customHeight="1" ht="17.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>85</v>
+      <c r="A7" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s" s="5">
+        <v>249</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>40</v>
@@ -1854,11 +2241,11 @@
       </c>
     </row>
     <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" t="s">
-        <v>86</v>
+      <c r="A8" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s" s="5">
+        <v>250</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>41</v>
@@ -1880,11 +2267,11 @@
       </c>
     </row>
     <row ht="25" r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
+      <c r="A9" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s" s="5">
+        <v>251</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>42</v>
@@ -1906,11 +2293,11 @@
       </c>
     </row>
     <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" t="s">
-        <v>88</v>
+      <c r="A10" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s" s="5">
+        <v>252</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -1932,11 +2319,11 @@
       </c>
     </row>
     <row ht="25" r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
+      <c r="A11" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s" s="5">
+        <v>253</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>43</v>
@@ -1958,11 +2345,11 @@
       </c>
     </row>
     <row ht="25" r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" t="s">
-        <v>90</v>
+      <c r="A12" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s" s="5">
+        <v>254</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>49</v>
@@ -1984,11 +2371,11 @@
       </c>
     </row>
     <row ht="25" r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
+      <c r="A13" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s" s="5">
+        <v>255</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>50</v>
@@ -2010,11 +2397,11 @@
       </c>
     </row>
     <row ht="25" r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>92</v>
+      <c r="A14" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s" s="5">
+        <v>256</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>51</v>
@@ -2036,11 +2423,11 @@
       </c>
     </row>
     <row ht="25" r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>93</v>
+      <c r="A15" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s" s="5">
+        <v>257</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>45</v>
@@ -2062,11 +2449,11 @@
       </c>
     </row>
     <row ht="25" r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
+      <c r="A16" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s" s="5">
+        <v>258</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>46</v>
@@ -2088,11 +2475,11 @@
       </c>
     </row>
     <row ht="25" r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" t="s">
-        <v>95</v>
+      <c r="A17" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s" s="5">
+        <v>259</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>47</v>
@@ -2114,11 +2501,11 @@
       </c>
     </row>
     <row ht="25" r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
+      <c r="A18" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s" s="5">
+        <v>260</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>48</v>
@@ -2140,11 +2527,11 @@
       </c>
     </row>
     <row ht="25" r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
+      <c r="A19" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s" s="5">
+        <v>261</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>64</v>
@@ -2163,11 +2550,11 @@
       </c>
     </row>
     <row ht="25" r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s">
-        <v>98</v>
+      <c r="A20" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s" s="5">
+        <v>262</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>66</v>
@@ -2189,11 +2576,11 @@
       </c>
     </row>
     <row ht="25" r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" t="s">
-        <v>99</v>
+      <c r="A21" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s" s="5">
+        <v>263</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>67</v>
@@ -2215,11 +2602,11 @@
       </c>
     </row>
     <row ht="25" r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s">
-        <v>100</v>
+      <c r="A22" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="5">
+        <v>264</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>68</v>
@@ -2241,11 +2628,11 @@
       </c>
     </row>
     <row ht="25" r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s">
-        <v>101</v>
+      <c r="A23" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="5">
+        <v>265</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>69</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Prod.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="310">
   <si>
     <t>Result</t>
   </si>
@@ -840,6 +840,138 @@
   </si>
   <si>
     <t>Thu Jul 09 11:08:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:03:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:04:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:22:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:30:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:31:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:37:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:55:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:00:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:10:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:46:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:47:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:48:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 22:59:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:00:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:01:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:34:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:35:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:36:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:36:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:37:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:37:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:39:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:39:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:40:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:41:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:41:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:42:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:42:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:43:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:43:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:44:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:44:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:46:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:46:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:47:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:48:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:49:45 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1456,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -1341,10 +1473,10 @@
     </row>
     <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="3">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -1361,10 +1493,10 @@
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -1381,10 +1513,10 @@
     </row>
     <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1404,7 +1536,7 @@
         <v>70</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>55</v>
@@ -1424,7 +1556,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1444,7 +1576,7 @@
         <v>70</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1464,7 +1596,7 @@
         <v>70</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1499,7 +1631,7 @@
         <v>70</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1519,10 +1651,10 @@
     </row>
     <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1542,10 +1674,10 @@
     </row>
     <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>38</v>
@@ -1568,7 +1700,7 @@
         <v>70</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1591,7 +1723,7 @@
         <v>70</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1614,7 +1746,7 @@
         <v>70</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>228</v>
+        <v>297</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1637,7 +1769,7 @@
         <v>70</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>229</v>
+        <v>298</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1660,7 +1792,7 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
@@ -1683,7 +1815,7 @@
         <v>70</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>231</v>
+        <v>300</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1706,7 +1838,7 @@
         <v>70</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>232</v>
+        <v>301</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1729,7 +1861,7 @@
         <v>70</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>57</v>
@@ -1752,7 +1884,7 @@
         <v>70</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>54</v>
@@ -1778,7 +1910,7 @@
         <v>70</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1801,7 +1933,7 @@
         <v>70</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1824,7 +1956,7 @@
         <v>70</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>237</v>
+        <v>306</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
@@ -1847,7 +1979,7 @@
         <v>70</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1870,7 +2002,7 @@
         <v>70</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1893,7 +2025,7 @@
         <v>70</v>
       </c>
       <c r="B27" t="s" s="3">
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>59</v>
